--- a/artfynd/S 3558-2023 artfynd.xlsx
+++ b/artfynd/S 3558-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75975186</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64660837</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64661558</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75975111</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75975141</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75975107</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75975204</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1534,6 +1574,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64660857</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75975110</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64661899</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1866,6 +1921,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87534483</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1981,6 +2041,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87534584</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2096,6 +2161,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87534694</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2211,6 +2281,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87534851</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2326,6 +2401,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87534863</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2441,6 +2521,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87534864</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2556,6 +2641,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87534876</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2671,6 +2761,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87534887</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2786,6 +2881,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87534926</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2901,6 +3001,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87535070</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3016,6 +3121,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87535096</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3131,6 +3241,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87535097</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3237,6 +3352,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69940044</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3343,6 +3463,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69940045</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3449,6 +3574,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69940047</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3564,6 +3694,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87534879</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3679,6 +3814,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87534925</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3785,6 +3925,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69940046</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3896,6 +4041,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87535202</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4005,6 +4155,11 @@
       <c r="AY31" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87535203</t>
         </is>
       </c>
     </row>
@@ -4117,6 +4272,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75975215</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4218,6 +4378,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75975105</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4338,8 +4503,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92119979</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>